--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5079,11 +5079,14 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
@@ -5174,7 +5177,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5200,11 +5203,14 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
@@ -5295,7 +5301,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5416,7 +5422,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5442,11 +5448,14 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5081,11 +5081,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5205,11 +5201,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5327,11 +5319,7 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Myrås, Pi lm</t>
@@ -5450,11 +5438,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
